--- a/Mantenimiento/excels/CAJAMARCA-JAEN-JAEN.xlsx
+++ b/Mantenimiento/excels/CAJAMARCA-JAEN-JAEN.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1212,11 +1142,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1264,11 +1189,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1316,11 +1236,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1368,11 +1283,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1419,11 +1329,6 @@
       </c>
       <c r="K19" t="n">
         <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/CAJAMARCA-JAEN-JAEN.xlsx
+++ b/Mantenimiento/excels/CAJAMARCA-JAEN-JAEN.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>001</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-5.70668</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-78.80727</v>
-      </c>
-      <c r="I2" t="n">
-        <v>736</v>
-      </c>
-      <c r="J2" t="n">
-        <v>31</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-5.70668</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-78.80727</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>006</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-5.71465</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-78.8062</v>
-      </c>
-      <c r="I3" t="n">
-        <v>614</v>
-      </c>
-      <c r="J3" t="n">
-        <v>29</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-5.71465</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-78.8062</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>010</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-5.7008</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-78.8112</v>
-      </c>
-      <c r="I4" t="n">
-        <v>395</v>
-      </c>
-      <c r="J4" t="n">
-        <v>17</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-5.7008</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-78.8112</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>011</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-5.7067</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-78.81270000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>455</v>
-      </c>
-      <c r="J5" t="n">
-        <v>18</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-5.7067</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-78.8127</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>17001</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-5.706852</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-78.81146200000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1024</v>
-      </c>
-      <c r="J6" t="n">
-        <v>42</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-5.706852</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-78.811462</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>16002</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-5.705158</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-78.813557</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1071</v>
-      </c>
-      <c r="J7" t="n">
-        <v>48</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-5.705158</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-78.813557</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>16004</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-5.7123</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-78.807</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1042</v>
-      </c>
-      <c r="J8" t="n">
-        <v>41</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-5.7123</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-78.807</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1042</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>16005 PEDRO EMILIO PAULET MOSTAJO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-5.714135</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-78.806462</v>
-      </c>
-      <c r="I9" t="n">
-        <v>730</v>
-      </c>
-      <c r="J9" t="n">
-        <v>32</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-5.714135</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-78.806462</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>16049 INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-5.7151</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-78.79640000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>957</v>
-      </c>
-      <c r="J10" t="n">
-        <v>45</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-5.7151</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-78.7964</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>17514</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-5.711251</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-78.80007999999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>408</v>
-      </c>
-      <c r="J11" t="n">
-        <v>17</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-5.711251</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-78.80008</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -986,20 +1074,30 @@
           <t>16006 CRISTO REY</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-5.7352</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-78.7903</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1373</v>
-      </c>
-      <c r="J12" t="n">
-        <v>69</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-5.7352</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-78.7903</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1033,20 +1131,30 @@
           <t>16001 RAMON CASTILLA Y MARQUEZADO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-5.70326</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-78.80670000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>781</v>
-      </c>
-      <c r="J13" t="n">
-        <v>44</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-5.70326</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-78.8067</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1080,20 +1188,30 @@
           <t>JAEN DE BRACAMOROS</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-5.70551</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-78.81331400000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1218</v>
-      </c>
-      <c r="J14" t="n">
-        <v>78</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-5.70551</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-78.813314</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1127,20 +1245,30 @@
           <t>VICTOR RAUL HAYA DE LA TORRE</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-5.714702</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-78.802982</v>
-      </c>
-      <c r="I15" t="n">
-        <v>667</v>
-      </c>
-      <c r="J15" t="n">
-        <v>37</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-5.714702</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-78.802982</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1174,20 +1302,30 @@
           <t>NAZARENO</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-5.70793</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-78.80804000000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>516</v>
-      </c>
-      <c r="J16" t="n">
-        <v>34</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-5.70793</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-78.80804</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1221,20 +1359,30 @@
           <t>APLICACION VICTOR ANDRES BELAUNDE</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-5.70395211134617</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-78.80553322502099</v>
-      </c>
-      <c r="I17" t="n">
-        <v>423</v>
-      </c>
-      <c r="J17" t="n">
-        <v>26</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-5.70395211134617</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-78.805533225021</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>423</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1268,20 +1416,30 @@
           <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-5.70615</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-78.80916999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>613</v>
-      </c>
-      <c r="J18" t="n">
-        <v>23</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-5.70615</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-78.80917</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1315,20 +1473,30 @@
           <t>KINDER GARDEN COLLEGE</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-5.70816</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-78.81608</v>
-      </c>
-      <c r="I19" t="n">
-        <v>329</v>
-      </c>
-      <c r="J19" t="n">
-        <v>16</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-5.70816</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-78.81608</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
